--- a/2_Semestre/BackEnd/Projeto-Livraria/livro.xlsx
+++ b/2_Semestre/BackEnd/Projeto-Livraria/livro.xlsx
@@ -518,12 +518,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D8CA50&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1CCA50&gt;&gt;</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88FC0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8FC0&gt;&gt;</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -534,7 +534,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88D60&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8D60&gt;&gt;</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -544,7 +544,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D83AD0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C3AD0&gt;&gt;</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -567,7 +567,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D169C0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D15A9C0&gt;&gt;</t>
         </is>
       </c>
       <c r="O2" t="n">
@@ -583,12 +583,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D8CA50&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1CCA50&gt;&gt;</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88FC0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8FC0&gt;&gt;</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -599,7 +599,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88D60&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8D60&gt;&gt;</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D83AD0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C3AD0&gt;&gt;</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -632,7 +632,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D169C0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D15A9C0&gt;&gt;</t>
         </is>
       </c>
       <c r="O3" t="n">
@@ -648,12 +648,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D8CA50&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1CCA50&gt;&gt;</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88FC0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8FC0&gt;&gt;</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -664,7 +664,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88D60&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8D60&gt;&gt;</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D83AD0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C3AD0&gt;&gt;</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -697,7 +697,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D169C0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D15A9C0&gt;&gt;</t>
         </is>
       </c>
       <c r="O4" t="n">
@@ -713,12 +713,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D8CA50&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1CCA50&gt;&gt;</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88FC0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8FC0&gt;&gt;</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -729,7 +729,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88D60&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8D60&gt;&gt;</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D83AD0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C3AD0&gt;&gt;</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -762,7 +762,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D169C0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D15A9C0&gt;&gt;</t>
         </is>
       </c>
       <c r="O5" t="n">
@@ -778,12 +778,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D8CA50&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1CCA50&gt;&gt;</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88FC0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8FC0&gt;&gt;</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -794,7 +794,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88D60&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8D60&gt;&gt;</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D83AD0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C3AD0&gt;&gt;</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -827,7 +827,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D169C0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D15A9C0&gt;&gt;</t>
         </is>
       </c>
       <c r="O6" t="n">
@@ -843,12 +843,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D8CA50&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1CCA50&gt;&gt;</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88FC0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8FC0&gt;&gt;</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -859,7 +859,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88D60&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8D60&gt;&gt;</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D83AD0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C3AD0&gt;&gt;</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -892,7 +892,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D169C0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D15A9C0&gt;&gt;</t>
         </is>
       </c>
       <c r="O7" t="n">
@@ -908,12 +908,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D8CA50&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1CCA50&gt;&gt;</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88FC0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8FC0&gt;&gt;</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -924,7 +924,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88D60&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8D60&gt;&gt;</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D83AD0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C3AD0&gt;&gt;</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -957,7 +957,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D169C0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D15A9C0&gt;&gt;</t>
         </is>
       </c>
       <c r="O8" t="n">
@@ -973,12 +973,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D8CA50&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1CCA50&gt;&gt;</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88FC0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8FC0&gt;&gt;</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -989,7 +989,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88D60&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8D60&gt;&gt;</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D83AD0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C3AD0&gt;&gt;</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D169C0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D15A9C0&gt;&gt;</t>
         </is>
       </c>
       <c r="O9" t="n">
@@ -1038,12 +1038,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D8CA50&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1CCA50&gt;&gt;</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88FC0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8FC0&gt;&gt;</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88D60&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8D60&gt;&gt;</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D83AD0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C3AD0&gt;&gt;</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D169C0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D15A9C0&gt;&gt;</t>
         </is>
       </c>
       <c r="O10" t="n">
@@ -1103,12 +1103,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D8CA50&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1CCA50&gt;&gt;</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88FC0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8FC0&gt;&gt;</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88D60&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8D60&gt;&gt;</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D83AD0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C3AD0&gt;&gt;</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D169C0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D15A9C0&gt;&gt;</t>
         </is>
       </c>
       <c r="O11" t="n">
@@ -1168,12 +1168,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D8CA50&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1CCA50&gt;&gt;</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88FC0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8FC0&gt;&gt;</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88D60&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8D60&gt;&gt;</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D83AD0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C3AD0&gt;&gt;</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D169C0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D15A9C0&gt;&gt;</t>
         </is>
       </c>
       <c r="O12" t="n">
@@ -1233,12 +1233,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D8CA50&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1CCA50&gt;&gt;</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88FC0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8FC0&gt;&gt;</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88D60&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8D60&gt;&gt;</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D83AD0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C3AD0&gt;&gt;</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -1282,7 +1282,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D169C0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D15A9C0&gt;&gt;</t>
         </is>
       </c>
       <c r="O13" t="n">
@@ -1298,12 +1298,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D8CA50&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1CCA50&gt;&gt;</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88FC0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8FC0&gt;&gt;</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88D60&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8D60&gt;&gt;</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D83AD0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C3AD0&gt;&gt;</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D169C0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D15A9C0&gt;&gt;</t>
         </is>
       </c>
       <c r="O14" t="n">
@@ -1363,12 +1363,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D8CA50&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1CCA50&gt;&gt;</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88FC0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8FC0&gt;&gt;</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88D60&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8D60&gt;&gt;</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D83AD0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C3AD0&gt;&gt;</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D169C0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D15A9C0&gt;&gt;</t>
         </is>
       </c>
       <c r="O15" t="n">
@@ -1428,12 +1428,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D8CA50&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1CCA50&gt;&gt;</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88FC0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8FC0&gt;&gt;</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88D60&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8D60&gt;&gt;</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D83AD0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C3AD0&gt;&gt;</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D169C0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D15A9C0&gt;&gt;</t>
         </is>
       </c>
       <c r="O16" t="n">
@@ -1493,12 +1493,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D8CA50&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1CCA50&gt;&gt;</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88FC0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8FC0&gt;&gt;</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88D60&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8D60&gt;&gt;</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D83AD0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C3AD0&gt;&gt;</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D169C0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D15A9C0&gt;&gt;</t>
         </is>
       </c>
       <c r="O17" t="n">
@@ -1558,12 +1558,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D8CA50&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1CCA50&gt;&gt;</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88FC0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8FC0&gt;&gt;</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88D60&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8D60&gt;&gt;</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D83AD0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C3AD0&gt;&gt;</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D169C0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D15A9C0&gt;&gt;</t>
         </is>
       </c>
       <c r="O18" t="n">
@@ -1623,12 +1623,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D8CA50&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1CCA50&gt;&gt;</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88FC0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8FC0&gt;&gt;</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88D60&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8D60&gt;&gt;</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D83AD0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C3AD0&gt;&gt;</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D169C0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D15A9C0&gt;&gt;</t>
         </is>
       </c>
       <c r="O19" t="n">
@@ -1688,12 +1688,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D8CA50&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1CCA50&gt;&gt;</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88FC0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8FC0&gt;&gt;</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88D60&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8D60&gt;&gt;</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D83AD0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C3AD0&gt;&gt;</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D169C0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D15A9C0&gt;&gt;</t>
         </is>
       </c>
       <c r="O20" t="n">
@@ -1753,12 +1753,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D8CA50&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1CCA50&gt;&gt;</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88FC0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8FC0&gt;&gt;</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88D60&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8D60&gt;&gt;</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D83AD0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C3AD0&gt;&gt;</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D169C0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D15A9C0&gt;&gt;</t>
         </is>
       </c>
       <c r="O21" t="n">
@@ -1818,12 +1818,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D8CA50&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1CCA50&gt;&gt;</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88FC0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8FC0&gt;&gt;</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88D60&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8D60&gt;&gt;</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D83AD0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C3AD0&gt;&gt;</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D169C0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D15A9C0&gt;&gt;</t>
         </is>
       </c>
       <c r="O22" t="n">
@@ -1883,12 +1883,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D8CA50&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1CCA50&gt;&gt;</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88FC0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8FC0&gt;&gt;</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88D60&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8D60&gt;&gt;</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D83AD0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C3AD0&gt;&gt;</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D169C0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D15A9C0&gt;&gt;</t>
         </is>
       </c>
       <c r="O23" t="n">
@@ -1948,12 +1948,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D8CA50&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1CCA50&gt;&gt;</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88FC0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8FC0&gt;&gt;</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88D60&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8D60&gt;&gt;</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D83AD0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C3AD0&gt;&gt;</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D169C0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D15A9C0&gt;&gt;</t>
         </is>
       </c>
       <c r="O24" t="n">
@@ -2013,12 +2013,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D8CA50&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1CCA50&gt;&gt;</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88FC0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8FC0&gt;&gt;</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88D60&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8D60&gt;&gt;</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D83AD0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C3AD0&gt;&gt;</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D169C0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D15A9C0&gt;&gt;</t>
         </is>
       </c>
       <c r="O25" t="n">
@@ -2078,12 +2078,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D8CA50&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1CCA50&gt;&gt;</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88FC0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8FC0&gt;&gt;</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88D60&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8D60&gt;&gt;</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D83AD0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C3AD0&gt;&gt;</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -2127,7 +2127,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D169C0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D15A9C0&gt;&gt;</t>
         </is>
       </c>
       <c r="O26" t="n">
@@ -2143,12 +2143,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D8CA50&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1CCA50&gt;&gt;</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88FC0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8FC0&gt;&gt;</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88D60&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8D60&gt;&gt;</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D83AD0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C3AD0&gt;&gt;</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D169C0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D15A9C0&gt;&gt;</t>
         </is>
       </c>
       <c r="O27" t="n">
@@ -2208,12 +2208,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D8CA50&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1CCA50&gt;&gt;</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88FC0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8FC0&gt;&gt;</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88D60&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8D60&gt;&gt;</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D83AD0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C3AD0&gt;&gt;</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D169C0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D15A9C0&gt;&gt;</t>
         </is>
       </c>
       <c r="O28" t="n">
@@ -2273,12 +2273,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D8CA50&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1CCA50&gt;&gt;</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88FC0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8FC0&gt;&gt;</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88D60&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8D60&gt;&gt;</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D83AD0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C3AD0&gt;&gt;</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D169C0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D15A9C0&gt;&gt;</t>
         </is>
       </c>
       <c r="O29" t="n">
@@ -2338,12 +2338,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D8CA50&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1CCA50&gt;&gt;</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88FC0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8FC0&gt;&gt;</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88D60&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8D60&gt;&gt;</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D83AD0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C3AD0&gt;&gt;</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -2387,7 +2387,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D169C0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D15A9C0&gt;&gt;</t>
         </is>
       </c>
       <c r="O30" t="n">
@@ -2403,12 +2403,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D8CA50&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1CCA50&gt;&gt;</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88FC0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8FC0&gt;&gt;</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -2419,7 +2419,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88D60&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8D60&gt;&gt;</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2429,7 +2429,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D83AD0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C3AD0&gt;&gt;</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D169C0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D15A9C0&gt;&gt;</t>
         </is>
       </c>
       <c r="O31" t="n">
@@ -2468,12 +2468,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D8CA50&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1CCA50&gt;&gt;</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88FC0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8FC0&gt;&gt;</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88D60&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8D60&gt;&gt;</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D83AD0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C3AD0&gt;&gt;</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -2517,7 +2517,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D169C0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D15A9C0&gt;&gt;</t>
         </is>
       </c>
       <c r="O32" t="n">
@@ -2533,12 +2533,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D8CA50&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1CCA50&gt;&gt;</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88FC0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8FC0&gt;&gt;</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88D60&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8D60&gt;&gt;</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D83AD0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C3AD0&gt;&gt;</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D169C0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D15A9C0&gt;&gt;</t>
         </is>
       </c>
       <c r="O33" t="n">
@@ -2598,12 +2598,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D8CA50&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1CCA50&gt;&gt;</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88FC0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8FC0&gt;&gt;</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88D60&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8D60&gt;&gt;</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D83AD0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C3AD0&gt;&gt;</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D169C0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D15A9C0&gt;&gt;</t>
         </is>
       </c>
       <c r="O34" t="n">
@@ -2663,12 +2663,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D8CA50&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1CCA50&gt;&gt;</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88FC0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8FC0&gt;&gt;</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88D60&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8D60&gt;&gt;</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D83AD0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C3AD0&gt;&gt;</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D169C0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D15A9C0&gt;&gt;</t>
         </is>
       </c>
       <c r="O35" t="n">
@@ -2728,12 +2728,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D8CA50&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1CCA50&gt;&gt;</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88FC0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8FC0&gt;&gt;</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88D60&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8D60&gt;&gt;</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D83AD0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C3AD0&gt;&gt;</t>
         </is>
       </c>
       <c r="H36" t="n">
@@ -2777,7 +2777,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D169C0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D15A9C0&gt;&gt;</t>
         </is>
       </c>
       <c r="O36" t="n">
@@ -2793,12 +2793,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D8CA50&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1CCA50&gt;&gt;</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88FC0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8FC0&gt;&gt;</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88D60&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8D60&gt;&gt;</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D83AD0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C3AD0&gt;&gt;</t>
         </is>
       </c>
       <c r="H37" t="n">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D169C0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D15A9C0&gt;&gt;</t>
         </is>
       </c>
       <c r="O37" t="n">
@@ -2858,12 +2858,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D8CA50&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1CCA50&gt;&gt;</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88FC0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8FC0&gt;&gt;</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -2874,7 +2874,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88D60&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8D60&gt;&gt;</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D83AD0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C3AD0&gt;&gt;</t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -2907,7 +2907,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D169C0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D15A9C0&gt;&gt;</t>
         </is>
       </c>
       <c r="O38" t="n">
@@ -2923,12 +2923,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D8CA50&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1CCA50&gt;&gt;</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88FC0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8FC0&gt;&gt;</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88D60&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8D60&gt;&gt;</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D83AD0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C3AD0&gt;&gt;</t>
         </is>
       </c>
       <c r="H39" t="n">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D169C0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D15A9C0&gt;&gt;</t>
         </is>
       </c>
       <c r="O39" t="n">
@@ -2988,12 +2988,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D8CA50&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1CCA50&gt;&gt;</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88FC0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8FC0&gt;&gt;</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -3004,7 +3004,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88D60&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8D60&gt;&gt;</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D83AD0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C3AD0&gt;&gt;</t>
         </is>
       </c>
       <c r="H40" t="n">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D169C0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D15A9C0&gt;&gt;</t>
         </is>
       </c>
       <c r="O40" t="n">
@@ -3053,12 +3053,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D8CA50&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1CCA50&gt;&gt;</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88FC0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8FC0&gt;&gt;</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88D60&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8D60&gt;&gt;</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D83AD0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C3AD0&gt;&gt;</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D169C0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D15A9C0&gt;&gt;</t>
         </is>
       </c>
       <c r="O41" t="n">
@@ -3118,12 +3118,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D8CA50&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1CCA50&gt;&gt;</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88FC0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8FC0&gt;&gt;</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -3134,7 +3134,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88D60&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8D60&gt;&gt;</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D83AD0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C3AD0&gt;&gt;</t>
         </is>
       </c>
       <c r="H42" t="n">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D169C0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D15A9C0&gt;&gt;</t>
         </is>
       </c>
       <c r="O42" t="n">
@@ -3183,12 +3183,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D8CA50&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1CCA50&gt;&gt;</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88FC0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8FC0&gt;&gt;</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -3199,7 +3199,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88D60&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8D60&gt;&gt;</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D83AD0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C3AD0&gt;&gt;</t>
         </is>
       </c>
       <c r="H43" t="n">
@@ -3232,7 +3232,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D169C0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D15A9C0&gt;&gt;</t>
         </is>
       </c>
       <c r="O43" t="n">
@@ -3248,12 +3248,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D8CA50&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1CCA50&gt;&gt;</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88FC0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8FC0&gt;&gt;</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88D60&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8D60&gt;&gt;</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D83AD0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C3AD0&gt;&gt;</t>
         </is>
       </c>
       <c r="H44" t="n">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D169C0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D15A9C0&gt;&gt;</t>
         </is>
       </c>
       <c r="O44" t="n">
@@ -3313,12 +3313,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D8CA50&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1CCA50&gt;&gt;</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88FC0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8FC0&gt;&gt;</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88D60&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8D60&gt;&gt;</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -3339,7 +3339,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D83AD0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C3AD0&gt;&gt;</t>
         </is>
       </c>
       <c r="H45" t="n">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D169C0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D15A9C0&gt;&gt;</t>
         </is>
       </c>
       <c r="O45" t="n">
@@ -3378,12 +3378,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D8CA50&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1CCA50&gt;&gt;</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88FC0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8FC0&gt;&gt;</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88D60&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8D60&gt;&gt;</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3404,7 +3404,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D83AD0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C3AD0&gt;&gt;</t>
         </is>
       </c>
       <c r="H46" t="n">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D169C0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D15A9C0&gt;&gt;</t>
         </is>
       </c>
       <c r="O46" t="n">
@@ -3443,12 +3443,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D8CA50&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1CCA50&gt;&gt;</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88FC0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8FC0&gt;&gt;</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -3459,7 +3459,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88D60&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8D60&gt;&gt;</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3469,7 +3469,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D83AD0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C3AD0&gt;&gt;</t>
         </is>
       </c>
       <c r="H47" t="n">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D169C0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D15A9C0&gt;&gt;</t>
         </is>
       </c>
       <c r="O47" t="n">
@@ -3508,12 +3508,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D8CA50&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1CCA50&gt;&gt;</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88FC0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8FC0&gt;&gt;</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88D60&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8D60&gt;&gt;</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D83AD0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C3AD0&gt;&gt;</t>
         </is>
       </c>
       <c r="H48" t="n">
@@ -3557,7 +3557,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D169C0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D15A9C0&gt;&gt;</t>
         </is>
       </c>
       <c r="O48" t="n">
@@ -3573,12 +3573,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D8CA50&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1CCA50&gt;&gt;</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88FC0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8FC0&gt;&gt;</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88D60&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8D60&gt;&gt;</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D83AD0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C3AD0&gt;&gt;</t>
         </is>
       </c>
       <c r="H49" t="n">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D169C0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D15A9C0&gt;&gt;</t>
         </is>
       </c>
       <c r="O49" t="n">
@@ -3638,12 +3638,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D8CA50&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1CCA50&gt;&gt;</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88FC0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8FC0&gt;&gt;</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88D60&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8D60&gt;&gt;</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D83AD0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C3AD0&gt;&gt;</t>
         </is>
       </c>
       <c r="H50" t="n">
@@ -3687,7 +3687,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D169C0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D15A9C0&gt;&gt;</t>
         </is>
       </c>
       <c r="O50" t="n">
@@ -3703,12 +3703,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D8CA50&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1CCA50&gt;&gt;</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88FC0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8FC0&gt;&gt;</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -3719,7 +3719,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D88D60&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C8D60&gt;&gt;</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D83AD0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D1C3AD0&gt;&gt;</t>
         </is>
       </c>
       <c r="H51" t="n">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000002AFF3D169C0&gt;&gt;</t>
+          <t>&lt;bound method StringMethods.strip of &lt;pandas.core.strings.accessor.StringMethods object at 0x000001A29D15A9C0&gt;&gt;</t>
         </is>
       </c>
       <c r="O51" t="n">
